--- a/Result/profitability/6216.xlsx
+++ b/Result/profitability/6216.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.52</v>
       </c>
       <c r="M2" t="n">
-        <v>0.25875</v>
+        <v>0.16625</v>
       </c>
       <c r="N2" t="n">
-        <v>45.45</v>
+        <v>44.82875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2625</v>
+        <v>0.21625</v>
       </c>
       <c r="N3" t="n">
-        <v>44.84125</v>
+        <v>44.31</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2625</v>
+        <v>0.2075</v>
       </c>
       <c r="N4" t="n">
-        <v>44.6425</v>
+        <v>44.42250000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.22875</v>
+        <v>0.2675</v>
       </c>
       <c r="N5" t="n">
-        <v>43.94750000000001</v>
+        <v>43.22375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2925</v>
+        <v>0.25</v>
       </c>
       <c r="N6" t="n">
-        <v>42.66999999999999</v>
+        <v>42.71250000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.54</v>
       </c>
       <c r="M7" t="n">
-        <v>0.32</v>
+        <v>0.29375</v>
       </c>
       <c r="N7" t="n">
-        <v>40.87</v>
+        <v>41.1175</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.51</v>
       </c>
       <c r="M8" t="n">
-        <v>0.36</v>
+        <v>0.3724999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>40.9375</v>
+        <v>41.10250000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6216</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>148</v>
+      </c>
+      <c r="D75" t="n">
+        <v>84</v>
+      </c>
+      <c r="E75" t="n">
+        <v>64</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.51%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.19125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>45.04125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03136882129277563</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9393939393939394</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.789999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1177068509859728</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
